--- a/data/Oficina_de_procuradora_de_mujeres/opmVictimas.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmVictimas.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242CC9AA-041F-4E97-9788-3E944235B490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3661CBA9-2093-44F0-9D8A-D92A2488C49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6528" yWindow="2148" windowWidth="17280" windowHeight="9420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="anual" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">anual!$A$1:$J$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">anual!$A$1:$A$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -489,7 +489,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -573,7 +573,7 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -651,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="C22">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -728,7 +728,7 @@
         <v>6</v>
       </c>
       <c r="C29">
-        <v>497</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -805,7 +805,7 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <v>373</v>
+        <v>875</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -963,6 +963,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Oficina_de_procuradora_de_mujeres/opmVictimas.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmVictimas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3661CBA9-2093-44F0-9D8A-D92A2488C49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBAEAE0-6666-4E89-BD7C-91C291A731F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9192" yWindow="1200" windowWidth="14352" windowHeight="9420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="anual" sheetId="1" r:id="rId1"/>
@@ -489,7 +489,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -573,7 +573,7 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -651,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="C22">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -728,7 +728,7 @@
         <v>6</v>
       </c>
       <c r="C29">
-        <v>1006</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -805,7 +805,7 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <v>875</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">

--- a/data/Oficina_de_procuradora_de_mujeres/opmVictimas.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmVictimas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBAEAE0-6666-4E89-BD7C-91C291A731F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B59A3D4-8432-4B3E-B0CA-48667160D9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9192" yWindow="1200" windowWidth="14352" windowHeight="9420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8340" yWindow="2304" windowWidth="12564" windowHeight="9384" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="anual" sheetId="1" r:id="rId1"/>
@@ -489,7 +489,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -573,7 +573,7 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -651,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="C22">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -728,7 +728,7 @@
         <v>6</v>
       </c>
       <c r="C29">
-        <v>1155</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -805,7 +805,7 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <v>1037</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
